--- a/data/Otoliths_Gatun.xlsx
+++ b/data/Otoliths_Gatun.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/svenpallacks/Documents/Academic_work/02_Postdoc/01_Projects/2026-Dillon-workshop-otoliths/04_Code/Example_2_clean/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/svenpallacks/Documents/Academic_work/02_Postdoc/01_Projects/2026-Dillon-workshop-otoliths/04_Code/Example_2_SvenGitHub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A88161-4550-6045-9CA2-F73D7CB6622D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B5B250-EF67-9444-99B5-BD1F16B5639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{59D30900-11EF-C545-ACFE-3C8B1B0E3139}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="34">
   <si>
     <t>Sample_ID</t>
   </si>
@@ -125,9 +125,6 @@
     <t>SP25-19-09</t>
   </si>
   <si>
-    <t>Channidae</t>
-  </si>
-  <si>
     <t>age_group</t>
   </si>
   <si>
@@ -135,6 +132,15 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Chaunacidae</t>
+  </si>
+  <si>
+    <t>Bregmacerotidae</t>
+  </si>
+  <si>
+    <t>Myctophidae</t>
   </si>
 </sst>
 </file>
@@ -530,19 +536,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9553F27D-8726-A340-8D09-76B17CD8D61E}">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -562,7 +568,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -582,7 +588,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -602,7 +608,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -622,7 +628,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -642,7 +648,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -662,7 +668,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -682,7 +688,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -702,7 +708,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -722,7 +728,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -742,7 +748,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -762,7 +768,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -782,7 +788,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -802,7 +808,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -822,7 +828,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -842,7 +848,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -862,7 +868,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -882,7 +888,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -902,7 +908,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
@@ -914,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" s="2">
         <v>0.68899999999999995</v>
@@ -922,7 +928,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>5</v>
@@ -942,7 +948,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>5</v>
@@ -962,7 +968,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>5</v>
@@ -982,7 +988,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>11</v>
@@ -1002,7 +1008,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>11</v>
@@ -1022,7 +1028,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>11</v>
@@ -1042,7 +1048,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>11</v>
@@ -1062,7 +1068,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>11</v>
@@ -1082,7 +1088,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>11</v>
@@ -1102,7 +1108,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>11</v>
@@ -1122,7 +1128,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>11</v>
@@ -1142,7 +1148,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>11</v>
@@ -1162,7 +1168,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>11</v>
@@ -1182,7 +1188,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>11</v>
@@ -1202,7 +1208,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
@@ -1222,7 +1228,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>11</v>
@@ -1242,7 +1248,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
@@ -1262,7 +1268,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
@@ -1282,7 +1288,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
@@ -1302,7 +1308,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
@@ -1322,7 +1328,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
@@ -1342,7 +1348,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>13</v>
@@ -1362,7 +1368,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>13</v>
@@ -1374,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F42" s="2">
         <v>0.76300000000000001</v>
@@ -1382,7 +1388,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>13</v>
@@ -1394,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F43" s="2">
         <v>0.752</v>
@@ -1402,7 +1408,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>13</v>
@@ -1414,7 +1420,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44" s="2">
         <v>1.081</v>
@@ -1422,7 +1428,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
@@ -1434,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F45" s="2">
         <v>0.84199999999999997</v>
@@ -1442,7 +1448,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>13</v>
@@ -1462,7 +1468,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
@@ -1482,7 +1488,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>13</v>
@@ -1502,7 +1508,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
@@ -1522,7 +1528,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>13</v>
@@ -1542,7 +1548,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
@@ -1562,7 +1568,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
@@ -1582,7 +1588,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
@@ -1602,7 +1608,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
@@ -1622,7 +1628,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
@@ -1642,7 +1648,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
@@ -1662,7 +1668,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
@@ -1682,7 +1688,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
@@ -1702,7 +1708,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>13</v>
@@ -1722,7 +1728,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>17</v>
@@ -1742,7 +1748,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>17</v>
@@ -1762,7 +1768,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>17</v>
@@ -1782,7 +1788,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>17</v>
@@ -1802,7 +1808,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>17</v>
@@ -1822,7 +1828,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>17</v>
@@ -1842,7 +1848,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>17</v>
@@ -1862,7 +1868,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>18</v>
@@ -1882,7 +1888,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>18</v>
@@ -1902,7 +1908,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>18</v>
@@ -1922,7 +1928,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>18</v>
@@ -1942,7 +1948,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>18</v>
@@ -1962,7 +1968,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>18</v>
@@ -1982,7 +1988,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>18</v>
@@ -2002,7 +2008,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>18</v>
@@ -2022,7 +2028,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>18</v>
@@ -2042,7 +2048,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>18</v>
@@ -2062,7 +2068,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>18</v>
@@ -2082,7 +2088,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>18</v>
@@ -2102,7 +2108,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>18</v>
@@ -2122,7 +2128,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>18</v>
@@ -2142,7 +2148,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>18</v>
@@ -2154,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F81" s="2">
         <v>1.034</v>
@@ -2162,7 +2168,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>18</v>
@@ -2182,7 +2188,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>21</v>
@@ -2202,7 +2208,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>21</v>
@@ -2222,7 +2228,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>21</v>
@@ -2242,7 +2248,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>21</v>
@@ -2254,7 +2260,7 @@
         <v>8</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F86" s="2">
         <v>1.1439999999999999</v>
@@ -2262,7 +2268,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>22</v>
@@ -2282,7 +2288,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>22</v>
@@ -2302,7 +2308,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>22</v>
@@ -2322,7 +2328,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>22</v>
@@ -2342,7 +2348,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>22</v>
@@ -2354,7 +2360,7 @@
         <v>8</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F91" s="2">
         <v>0.88600000000000001</v>
@@ -2362,7 +2368,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>22</v>
@@ -2374,7 +2380,7 @@
         <v>8</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F92" s="2">
         <v>0.75</v>
@@ -2382,7 +2388,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>22</v>
@@ -2402,7 +2408,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>22</v>
@@ -2422,7 +2428,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>22</v>
@@ -2442,7 +2448,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>22</v>
@@ -2462,7 +2468,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>22</v>
@@ -2482,7 +2488,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>25</v>
@@ -2502,7 +2508,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>25</v>
@@ -2522,7 +2528,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>25</v>
@@ -2542,7 +2548,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>25</v>
@@ -2562,7 +2568,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>25</v>
@@ -2582,7 +2588,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>25</v>
@@ -2602,7 +2608,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>25</v>
@@ -2622,7 +2628,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>25</v>
@@ -2642,7 +2648,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>25</v>
@@ -2662,7 +2668,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>25</v>
@@ -2682,7 +2688,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>25</v>
@@ -2702,7 +2708,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>25</v>
@@ -2722,7 +2728,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>27</v>
@@ -2742,7 +2748,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>27</v>
@@ -2762,7 +2768,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -2782,7 +2788,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>27</v>
@@ -2802,7 +2808,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>27</v>
@@ -2822,7 +2828,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
@@ -2842,7 +2848,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
@@ -2862,7 +2868,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
@@ -2882,7 +2888,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>27</v>
@@ -2902,7 +2908,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>27</v>
@@ -2922,7 +2928,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>27</v>
@@ -2942,7 +2948,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>27</v>
@@ -2962,7 +2968,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>27</v>
@@ -2982,7 +2988,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>27</v>
@@ -3002,7 +3008,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>27</v>
@@ -3022,7 +3028,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>27</v>
@@ -3042,7 +3048,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>27</v>
@@ -3062,7 +3068,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>27</v>
@@ -3082,7 +3088,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>27</v>
@@ -3102,7 +3108,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>27</v>
@@ -3122,7 +3128,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>27</v>
@@ -3142,7 +3148,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>27</v>
@@ -3162,7 +3168,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>27</v>
@@ -3182,7 +3188,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>27</v>
@@ -3191,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E133" s="4">
         <v>0.98099999999999998</v>
@@ -3202,7 +3208,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>27</v>
@@ -3222,7 +3228,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>27</v>
@@ -3242,7 +3248,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>27</v>
@@ -3258,6 +3264,966 @@
       </c>
       <c r="F136" s="2">
         <v>1.4710000000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E137" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="F137" s="2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>29</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="2">
+        <v>2</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E138" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="F138" s="2">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C139" s="2">
+        <v>3</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E139" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="F139" s="2">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>29</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="2">
+        <v>4</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E140" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="F140" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="2">
+        <v>5</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E141" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="F141" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>29</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="2">
+        <v>6</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E142" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="F142" s="2">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>29</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="2">
+        <v>7</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E143" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="F143" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="2">
+        <v>8</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E144" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="F144" s="2">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>29</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="2">
+        <v>9</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E145" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="F145" s="2">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>29</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="2">
+        <v>10</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E146" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="F146" s="2">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>29</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="2">
+        <v>11</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E147" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="F147" s="2">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="2">
+        <v>12</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E148" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F148" s="2">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>29</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="2">
+        <v>13</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E149" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="F149" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="2">
+        <v>14</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E150" s="2">
+        <v>0.89</v>
+      </c>
+      <c r="F150" s="2">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>29</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="2">
+        <v>15</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E151" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="F151" s="2">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>29</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="2">
+        <v>16</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E152" s="2">
+        <v>0.71</v>
+      </c>
+      <c r="F152" s="2">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>29</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="2">
+        <v>1</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E153" s="2">
+        <v>1.07</v>
+      </c>
+      <c r="F153" s="2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>29</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="2">
+        <v>2</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E154" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="F154" s="2">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>29</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="2">
+        <v>3</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E155" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F155" s="2">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>29</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="2">
+        <v>4</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E156" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F156" s="2">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>29</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="2">
+        <v>5</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E157" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F157" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>29</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" s="2">
+        <v>6</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E158" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F158" s="2">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>29</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" s="2">
+        <v>7</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E159" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="F159" s="2">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>29</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="2">
+        <v>8</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E160" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="F160" s="2">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>29</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="2">
+        <v>9</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E161" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="F161" s="2">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>29</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" s="2">
+        <v>1</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E162" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="F162" s="2">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>29</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" s="2">
+        <v>2</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E163" s="2">
+        <v>1.04</v>
+      </c>
+      <c r="F163" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>29</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C164" s="2">
+        <v>1</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E164" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="F164" s="2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>29</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" s="2">
+        <v>1</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E165" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F165" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>29</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" s="2">
+        <v>2</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E166" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F166" s="2">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>29</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C167" s="2">
+        <v>1</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E167" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="F167" s="2">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>29</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="2">
+        <v>1</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E168" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="F168" s="2">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>29</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="2">
+        <v>2</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E169" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="F169" s="2">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>29</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="2">
+        <v>3</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E170" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="F170" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>29</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="2">
+        <v>4</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E171" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="F171" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>29</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C172" s="2">
+        <v>1</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E172" s="2">
+        <v>0.83</v>
+      </c>
+      <c r="F172" s="2">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>29</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C173" s="2">
+        <v>2</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E173" s="2">
+        <v>1.17</v>
+      </c>
+      <c r="F173" s="2">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>29</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C174" s="2">
+        <v>3</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E174" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="F174" s="2">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>29</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C175" s="2">
+        <v>4</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E175" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="F175" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>29</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C176" s="2">
+        <v>1</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E176" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="F176" s="2">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>29</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C177" s="2">
+        <v>2</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E177" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="F177" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>29</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C178" s="2">
+        <v>3</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E178" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F178" s="2">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>29</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C179" s="2">
+        <v>4</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E179" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="F179" s="2">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>29</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180" s="2">
+        <v>5</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E180" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="F180" s="2">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>29</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C181" s="2">
+        <v>6</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E181" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F181" s="2">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>29</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C182" s="2">
+        <v>7</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E182" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="F182" s="2">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>29</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C183" s="2">
+        <v>8</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E183" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F183" s="2">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>29</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C184" s="2">
+        <v>1</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E184" s="2">
+        <v>1.01</v>
+      </c>
+      <c r="F184" s="2">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>
